--- a/data/credit_bond_all_2026-09-01.xlsx
+++ b/data/credit_bond_all_2026-09-01.xlsx
@@ -12744,12 +12744,8 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U54" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -12883,9 +12879,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AZ54" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ54" s="3"/>
     </row>
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
